--- a/artfynd/A 11987-2024 artfynd.xlsx
+++ b/artfynd/A 11987-2024 artfynd.xlsx
@@ -2174,10 +2174,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117964461</v>
+        <v>117963728</v>
       </c>
       <c r="B15" t="n">
-        <v>79561</v>
+        <v>57287</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2190,34 +2190,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592582</v>
+        <v>592616</v>
       </c>
       <c r="R15" t="n">
-        <v>6983052</v>
+        <v>6982971</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2249,7 +2254,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2259,7 +2264,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,22 +2279,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117963728</v>
+        <v>117964461</v>
       </c>
       <c r="B16" t="n">
-        <v>57287</v>
+        <v>79561</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2302,39 +2307,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592616</v>
+        <v>592582</v>
       </c>
       <c r="R16" t="n">
-        <v>6982971</v>
+        <v>6983052</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2391,22 +2391,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117980670</v>
+        <v>117980599</v>
       </c>
       <c r="B17" t="n">
-        <v>97836</v>
+        <v>90499</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2415,42 +2415,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592638</v>
+        <v>592686</v>
       </c>
       <c r="R17" t="n">
-        <v>6982928</v>
+        <v>6982827</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2509,10 +2505,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117980599</v>
+        <v>117980670</v>
       </c>
       <c r="B18" t="n">
-        <v>90499</v>
+        <v>97836</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2521,38 +2517,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592686</v>
+        <v>592638</v>
       </c>
       <c r="R18" t="n">
-        <v>6982827</v>
+        <v>6982928</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -3575,10 +3575,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117968554</v>
+        <v>117962093</v>
       </c>
       <c r="B28" t="n">
-        <v>57287</v>
+        <v>79561</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3591,39 +3591,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
+          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592461</v>
+        <v>592840</v>
       </c>
       <c r="R28" t="n">
-        <v>6982622</v>
+        <v>6982539</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3655,7 +3650,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3665,7 +3660,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3692,10 +3687,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117962093</v>
+        <v>117968554</v>
       </c>
       <c r="B29" t="n">
-        <v>79561</v>
+        <v>57287</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3708,34 +3703,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
+          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592840</v>
+        <v>592461</v>
       </c>
       <c r="R29" t="n">
-        <v>6982539</v>
+        <v>6982622</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -6267,10 +6267,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117980603</v>
+        <v>117980646</v>
       </c>
       <c r="B52" t="n">
-        <v>57287</v>
+        <v>79561</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6283,42 +6283,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>593009</v>
+        <v>592988</v>
       </c>
       <c r="R52" t="n">
-        <v>6982552</v>
+        <v>6982524</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6377,10 +6369,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117980646</v>
+        <v>117980603</v>
       </c>
       <c r="B53" t="n">
-        <v>79561</v>
+        <v>57287</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6393,34 +6385,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>592988</v>
+        <v>593009</v>
       </c>
       <c r="R53" t="n">
-        <v>6982524</v>
+        <v>6982552</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -8111,10 +8111,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117980698</v>
+        <v>117980629</v>
       </c>
       <c r="B70" t="n">
-        <v>97753</v>
+        <v>96791</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8127,21 +8127,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8151,10 +8151,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>593522</v>
+        <v>592189</v>
       </c>
       <c r="R70" t="n">
-        <v>6982157</v>
+        <v>6982694</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -8181,12 +8181,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8213,10 +8213,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117980629</v>
+        <v>117980698</v>
       </c>
       <c r="B71" t="n">
-        <v>96791</v>
+        <v>97753</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8229,21 +8229,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8253,10 +8253,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>592189</v>
+        <v>593522</v>
       </c>
       <c r="R71" t="n">
-        <v>6982694</v>
+        <v>6982157</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -8283,12 +8283,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 11987-2024 artfynd.xlsx
+++ b/artfynd/A 11987-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117963692</v>
+        <v>117963728</v>
       </c>
       <c r="B2" t="n">
         <v>57287</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592600</v>
+        <v>592616</v>
       </c>
       <c r="R2" t="n">
-        <v>6982942</v>
+        <v>6982971</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117963780</v>
+        <v>117964594</v>
       </c>
       <c r="B3" t="n">
-        <v>97836</v>
+        <v>79561</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,42 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592591</v>
+        <v>592544</v>
       </c>
       <c r="R3" t="n">
-        <v>6982977</v>
+        <v>6983091</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,12 +892,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1020,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117964594</v>
+        <v>117963209</v>
       </c>
       <c r="B5" t="n">
-        <v>79561</v>
+        <v>97836</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,38 +1028,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592544</v>
+        <v>592669</v>
       </c>
       <c r="R5" t="n">
-        <v>6983091</v>
+        <v>6982881</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,19 +1120,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117963188</v>
+        <v>117963272</v>
       </c>
       <c r="B6" t="n">
         <v>97836</v>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592688</v>
+        <v>592646</v>
       </c>
       <c r="R6" t="n">
-        <v>6982873</v>
+        <v>6982919</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,19 +1236,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117963307</v>
+        <v>117963188</v>
       </c>
       <c r="B7" t="n">
         <v>97836</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592647</v>
+        <v>592688</v>
       </c>
       <c r="R7" t="n">
-        <v>6982916</v>
+        <v>6982873</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,12 +1352,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117963141</v>
+        <v>117963446</v>
       </c>
       <c r="B9" t="n">
-        <v>78480</v>
+        <v>97836</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,38 +1493,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592684</v>
+        <v>592644</v>
       </c>
       <c r="R9" t="n">
-        <v>6982863</v>
+        <v>6982918</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,7 +1560,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1566,7 +1570,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,22 +1585,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117963209</v>
+        <v>117963692</v>
       </c>
       <c r="B10" t="n">
-        <v>97836</v>
+        <v>57287</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,30 +1609,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1637,10 +1642,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592669</v>
+        <v>592600</v>
       </c>
       <c r="R10" t="n">
-        <v>6982881</v>
+        <v>6982942</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,7 +1677,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1682,7 +1687,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,22 +1702,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117963272</v>
+        <v>117964461</v>
       </c>
       <c r="B11" t="n">
-        <v>97836</v>
+        <v>79561</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,42 +1726,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592646</v>
+        <v>592582</v>
       </c>
       <c r="R11" t="n">
-        <v>6982919</v>
+        <v>6983052</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1789,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1799,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,7 +1826,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117963517</v>
+        <v>117963307</v>
       </c>
       <c r="B12" t="n">
         <v>97836</v>
@@ -1860,7 +1861,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1869,7 +1870,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592623</v>
+        <v>592647</v>
       </c>
       <c r="R12" t="n">
         <v>6982916</v>
@@ -1904,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,7 +1915,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,7 +1942,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117963446</v>
+        <v>117963780</v>
       </c>
       <c r="B13" t="n">
         <v>97836</v>
@@ -1976,7 +1977,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1985,10 +1986,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592644</v>
+        <v>592591</v>
       </c>
       <c r="R13" t="n">
-        <v>6982918</v>
+        <v>6982977</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2030,7 +2031,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,12 +2046,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2174,10 +2175,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117963728</v>
+        <v>117963517</v>
       </c>
       <c r="B15" t="n">
-        <v>57287</v>
+        <v>97836</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2186,31 +2187,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592616</v>
+        <v>592623</v>
       </c>
       <c r="R15" t="n">
-        <v>6982971</v>
+        <v>6982916</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2279,22 +2279,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117964461</v>
+        <v>117963141</v>
       </c>
       <c r="B16" t="n">
-        <v>79561</v>
+        <v>78480</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2307,21 +2307,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592582</v>
+        <v>592684</v>
       </c>
       <c r="R16" t="n">
-        <v>6983052</v>
+        <v>6982863</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2391,22 +2391,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117980599</v>
+        <v>117980681</v>
       </c>
       <c r="B17" t="n">
-        <v>90499</v>
+        <v>90517</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2419,21 +2419,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592686</v>
+        <v>592612</v>
       </c>
       <c r="R17" t="n">
-        <v>6982827</v>
+        <v>6982945</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117980670</v>
+        <v>117980585</v>
       </c>
       <c r="B18" t="n">
-        <v>97836</v>
+        <v>90464</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2517,42 +2517,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592638</v>
+        <v>592687</v>
       </c>
       <c r="R18" t="n">
-        <v>6982928</v>
+        <v>6982838</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2611,10 +2607,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117984731</v>
+        <v>117980711</v>
       </c>
       <c r="B19" t="n">
-        <v>97836</v>
+        <v>86816</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2623,45 +2619,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592704</v>
+        <v>592627</v>
       </c>
       <c r="R19" t="n">
-        <v>6982987</v>
+        <v>6982939</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2693,40 +2685,34 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>100-tals plantor</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117980604</v>
+        <v>117984731</v>
       </c>
       <c r="B20" t="n">
-        <v>57287</v>
+        <v>97836</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2735,49 +2721,45 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Lillsjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592585</v>
+        <v>592704</v>
       </c>
       <c r="R20" t="n">
-        <v>6982972</v>
+        <v>6982987</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2809,34 +2791,40 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>100-tals plantor</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117980711</v>
+        <v>117980685</v>
       </c>
       <c r="B21" t="n">
-        <v>86816</v>
+        <v>78480</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2849,21 +2837,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2873,10 +2861,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592627</v>
+        <v>592676</v>
       </c>
       <c r="R21" t="n">
-        <v>6982939</v>
+        <v>6982878</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2935,10 +2923,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117980685</v>
+        <v>117980604</v>
       </c>
       <c r="B22" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2951,34 +2939,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592676</v>
+        <v>592585</v>
       </c>
       <c r="R22" t="n">
-        <v>6982878</v>
+        <v>6982972</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3037,10 +3033,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117980681</v>
+        <v>117980670</v>
       </c>
       <c r="B23" t="n">
-        <v>90517</v>
+        <v>97836</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3049,38 +3045,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592612</v>
+        <v>592638</v>
       </c>
       <c r="R23" t="n">
-        <v>6982945</v>
+        <v>6982928</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117980584</v>
+        <v>117980599</v>
       </c>
       <c r="B24" t="n">
-        <v>90464</v>
+        <v>90499</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3151,25 +3151,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592541</v>
+        <v>592686</v>
       </c>
       <c r="R24" t="n">
-        <v>6983087</v>
+        <v>6982827</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3241,7 +3241,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117980585</v>
+        <v>117980584</v>
       </c>
       <c r="B25" t="n">
         <v>90464</v>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592687</v>
+        <v>592541</v>
       </c>
       <c r="R25" t="n">
-        <v>6982838</v>
+        <v>6983087</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3343,10 +3343,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117961348</v>
+        <v>117967502</v>
       </c>
       <c r="B26" t="n">
-        <v>97836</v>
+        <v>56491</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3355,42 +3355,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
+          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592940</v>
+        <v>592195</v>
       </c>
       <c r="R26" t="n">
-        <v>6982496</v>
+        <v>6982742</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3422,7 +3423,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3432,7 +3433,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3447,22 +3448,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117961947</v>
+        <v>117967766</v>
       </c>
       <c r="B27" t="n">
-        <v>97836</v>
+        <v>58102</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3471,42 +3472,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
+          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592880</v>
+        <v>592164</v>
       </c>
       <c r="R27" t="n">
-        <v>6982514</v>
+        <v>6982658</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3538,7 +3535,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3548,7 +3545,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3575,10 +3572,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117962093</v>
+        <v>117961816</v>
       </c>
       <c r="B28" t="n">
-        <v>79561</v>
+        <v>97836</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3587,38 +3584,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592840</v>
+        <v>592880</v>
       </c>
       <c r="R28" t="n">
-        <v>6982539</v>
+        <v>6982501</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3650,7 +3651,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3660,7 +3661,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3687,10 +3688,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117968554</v>
+        <v>117962504</v>
       </c>
       <c r="B29" t="n">
-        <v>57287</v>
+        <v>97753</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3699,43 +3700,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
+          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592461</v>
+        <v>592749</v>
       </c>
       <c r="R29" t="n">
-        <v>6982622</v>
+        <v>6982429</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3767,7 +3763,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3777,7 +3773,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3792,22 +3788,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117962152</v>
+        <v>117961947</v>
       </c>
       <c r="B30" t="n">
-        <v>57287</v>
+        <v>97836</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3816,31 +3812,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3849,10 +3844,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592878</v>
+        <v>592880</v>
       </c>
       <c r="R30" t="n">
-        <v>6982510</v>
+        <v>6982514</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3884,7 +3879,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3894,7 +3889,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3909,22 +3904,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117967986</v>
+        <v>117967797</v>
       </c>
       <c r="B31" t="n">
-        <v>57287</v>
+        <v>79561</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3937,39 +3932,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svarttjärnen (Svarttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592321</v>
+        <v>592219</v>
       </c>
       <c r="R31" t="n">
-        <v>6982713</v>
+        <v>6982668</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4001,7 +3991,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4011,7 +4001,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4038,10 +4028,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117967797</v>
+        <v>117967729</v>
       </c>
       <c r="B32" t="n">
-        <v>79561</v>
+        <v>97740</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4050,25 +4040,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4078,10 +4068,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592219</v>
+        <v>592204</v>
       </c>
       <c r="R32" t="n">
-        <v>6982668</v>
+        <v>6982667</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4113,7 +4103,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4123,7 +4113,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4150,10 +4140,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117961466</v>
+        <v>117969135</v>
       </c>
       <c r="B33" t="n">
-        <v>57287</v>
+        <v>97836</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4162,36 +4152,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4200,10 +4184,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592958</v>
+        <v>593016</v>
       </c>
       <c r="R33" t="n">
-        <v>6982498</v>
+        <v>6982493</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4235,7 +4219,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4245,7 +4229,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4272,7 +4256,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117967502</v>
+        <v>117968088</v>
       </c>
       <c r="B34" t="n">
         <v>56491</v>
@@ -4317,10 +4301,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592195</v>
+        <v>592312</v>
       </c>
       <c r="R34" t="n">
-        <v>6982742</v>
+        <v>6982681</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4352,7 +4336,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4362,7 +4346,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4389,10 +4373,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117968088</v>
+        <v>117961605</v>
       </c>
       <c r="B35" t="n">
-        <v>56491</v>
+        <v>57287</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4405,16 +4389,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4425,22 +4409,22 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
+          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>592312</v>
+        <v>592958</v>
       </c>
       <c r="R35" t="n">
-        <v>6982681</v>
+        <v>6982499</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4469,7 +4453,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4479,7 +4463,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4506,10 +4490,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117961605</v>
+        <v>117961348</v>
       </c>
       <c r="B36" t="n">
-        <v>57287</v>
+        <v>97836</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4518,31 +4502,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4551,13 +4534,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>592958</v>
+        <v>592940</v>
       </c>
       <c r="R36" t="n">
-        <v>6982499</v>
+        <v>6982496</v>
       </c>
       <c r="S36" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4586,7 +4569,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4596,7 +4579,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4611,22 +4594,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117967766</v>
+        <v>117961466</v>
       </c>
       <c r="B37" t="n">
-        <v>58102</v>
+        <v>57287</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4635,20 +4618,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>208245</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4657,16 +4640,26 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
+          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>592164</v>
+        <v>592958</v>
       </c>
       <c r="R37" t="n">
-        <v>6982658</v>
+        <v>6982498</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4698,7 +4691,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4708,7 +4701,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4735,10 +4728,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117962504</v>
+        <v>117962093</v>
       </c>
       <c r="B38" t="n">
-        <v>97753</v>
+        <v>79561</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4747,25 +4740,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4775,10 +4768,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>592749</v>
+        <v>592840</v>
       </c>
       <c r="R38" t="n">
-        <v>6982429</v>
+        <v>6982539</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4810,7 +4803,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4820,7 +4813,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4835,22 +4828,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117969135</v>
+        <v>117962294</v>
       </c>
       <c r="B39" t="n">
-        <v>97836</v>
+        <v>91962</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4859,42 +4852,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>593016</v>
+        <v>592811</v>
       </c>
       <c r="R39" t="n">
-        <v>6982493</v>
+        <v>6982463</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4926,7 +4915,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4936,7 +4925,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5075,10 +5064,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117962294</v>
+        <v>117962152</v>
       </c>
       <c r="B41" t="n">
-        <v>91962</v>
+        <v>57287</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5091,34 +5080,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>592811</v>
+        <v>592878</v>
       </c>
       <c r="R41" t="n">
-        <v>6982463</v>
+        <v>6982510</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5150,7 +5144,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5160,7 +5154,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5175,22 +5169,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117967729</v>
+        <v>117967986</v>
       </c>
       <c r="B42" t="n">
-        <v>97740</v>
+        <v>57287</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5199,38 +5193,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Svarttjärnen (Svarttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>592204</v>
+        <v>592321</v>
       </c>
       <c r="R42" t="n">
-        <v>6982667</v>
+        <v>6982713</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5262,7 +5261,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5272,7 +5271,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5299,10 +5298,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117961816</v>
+        <v>117968554</v>
       </c>
       <c r="B43" t="n">
-        <v>97836</v>
+        <v>57287</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5311,42 +5310,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
+          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>592880</v>
+        <v>592461</v>
       </c>
       <c r="R43" t="n">
-        <v>6982501</v>
+        <v>6982622</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5415,10 +5415,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117980648</v>
+        <v>117980594</v>
       </c>
       <c r="B44" t="n">
-        <v>79561</v>
+        <v>79098</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5431,21 +5431,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>592971</v>
+        <v>593185</v>
       </c>
       <c r="R44" t="n">
-        <v>6982531</v>
+        <v>6982435</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5517,10 +5517,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117980607</v>
+        <v>117980642</v>
       </c>
       <c r="B45" t="n">
-        <v>57287</v>
+        <v>79561</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5533,46 +5533,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>592961</v>
+        <v>592468</v>
       </c>
       <c r="R45" t="n">
-        <v>6982496</v>
+        <v>6982583</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5599,12 +5587,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5631,10 +5619,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117980608</v>
+        <v>117980600</v>
       </c>
       <c r="B46" t="n">
-        <v>57287</v>
+        <v>90499</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5647,42 +5635,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>593293</v>
+        <v>592949</v>
       </c>
       <c r="R46" t="n">
-        <v>6982240</v>
+        <v>6982497</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5709,12 +5689,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5741,10 +5721,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117980609</v>
+        <v>117980644</v>
       </c>
       <c r="B47" t="n">
-        <v>57287</v>
+        <v>79561</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5757,42 +5737,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>593267</v>
+        <v>592186</v>
       </c>
       <c r="R47" t="n">
-        <v>6982373</v>
+        <v>6982718</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5819,12 +5791,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5851,10 +5823,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117980641</v>
+        <v>117980666</v>
       </c>
       <c r="B48" t="n">
-        <v>79561</v>
+        <v>78216</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5867,21 +5839,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5891,10 +5863,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>592490</v>
+        <v>593185</v>
       </c>
       <c r="R48" t="n">
-        <v>6982570</v>
+        <v>6982435</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5921,12 +5893,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5953,7 +5925,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117980647</v>
+        <v>117980643</v>
       </c>
       <c r="B49" t="n">
         <v>79561</v>
@@ -5993,10 +5965,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>592968</v>
+        <v>592231</v>
       </c>
       <c r="R49" t="n">
-        <v>6982522</v>
+        <v>6982683</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6023,12 +5995,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6055,10 +6027,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117980655</v>
+        <v>117980667</v>
       </c>
       <c r="B50" t="n">
-        <v>79561</v>
+        <v>78216</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6071,21 +6043,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6095,10 +6067,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>593130</v>
+        <v>593125</v>
       </c>
       <c r="R50" t="n">
-        <v>6982511</v>
+        <v>6982518</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6157,10 +6129,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117980624</v>
+        <v>117980648</v>
       </c>
       <c r="B51" t="n">
-        <v>57303</v>
+        <v>79561</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6173,42 +6145,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>592180</v>
+        <v>592971</v>
       </c>
       <c r="R51" t="n">
-        <v>6982742</v>
+        <v>6982531</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6235,12 +6199,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6369,10 +6333,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117980603</v>
+        <v>117980624</v>
       </c>
       <c r="B53" t="n">
-        <v>57287</v>
+        <v>57303</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6385,16 +6349,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6417,10 +6381,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>593009</v>
+        <v>592180</v>
       </c>
       <c r="R53" t="n">
-        <v>6982552</v>
+        <v>6982742</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6479,10 +6443,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117980712</v>
+        <v>117980601</v>
       </c>
       <c r="B54" t="n">
-        <v>79596</v>
+        <v>90499</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6491,25 +6455,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6519,10 +6483,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>593140</v>
+        <v>593259</v>
       </c>
       <c r="R54" t="n">
-        <v>6982464</v>
+        <v>6982361</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6581,10 +6545,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117980586</v>
+        <v>117980707</v>
       </c>
       <c r="B55" t="n">
-        <v>90464</v>
+        <v>91772</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6597,21 +6561,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6621,10 +6585,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>593268</v>
+        <v>592286</v>
       </c>
       <c r="R55" t="n">
-        <v>6982369</v>
+        <v>6982699</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6651,12 +6615,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6683,10 +6647,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117980644</v>
+        <v>117980608</v>
       </c>
       <c r="B56" t="n">
-        <v>79561</v>
+        <v>57287</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6699,34 +6663,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>592186</v>
+        <v>593293</v>
       </c>
       <c r="R56" t="n">
-        <v>6982718</v>
+        <v>6982240</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6753,12 +6725,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6785,10 +6757,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117980621</v>
+        <v>117980609</v>
       </c>
       <c r="B57" t="n">
-        <v>79590</v>
+        <v>57287</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6797,38 +6769,46 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>593140</v>
+        <v>593267</v>
       </c>
       <c r="R57" t="n">
-        <v>6982464</v>
+        <v>6982373</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6887,10 +6867,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117980653</v>
+        <v>117980597</v>
       </c>
       <c r="B58" t="n">
-        <v>79561</v>
+        <v>79069</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6903,21 +6883,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6927,10 +6907,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>593140</v>
+        <v>593125</v>
       </c>
       <c r="R58" t="n">
-        <v>6982464</v>
+        <v>6982518</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6989,10 +6969,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117980620</v>
+        <v>117980645</v>
       </c>
       <c r="B59" t="n">
-        <v>79590</v>
+        <v>79561</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7001,25 +6981,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7029,10 +7009,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>592968</v>
+        <v>592168</v>
       </c>
       <c r="R59" t="n">
-        <v>6982522</v>
+        <v>6982756</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7059,12 +7039,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7091,10 +7071,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117980645</v>
+        <v>117980586</v>
       </c>
       <c r="B60" t="n">
-        <v>79561</v>
+        <v>90464</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7103,25 +7083,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7131,10 +7111,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>592168</v>
+        <v>593268</v>
       </c>
       <c r="R60" t="n">
-        <v>6982756</v>
+        <v>6982369</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7161,12 +7141,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7193,10 +7173,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117980642</v>
+        <v>117980621</v>
       </c>
       <c r="B61" t="n">
-        <v>79561</v>
+        <v>79590</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7205,25 +7185,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7233,10 +7213,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>592468</v>
+        <v>593140</v>
       </c>
       <c r="R61" t="n">
-        <v>6982583</v>
+        <v>6982464</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7263,12 +7243,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7295,10 +7275,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117980694</v>
+        <v>117980607</v>
       </c>
       <c r="B62" t="n">
-        <v>97753</v>
+        <v>57287</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7307,38 +7287,50 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>592218</v>
+        <v>592961</v>
       </c>
       <c r="R62" t="n">
-        <v>6982683</v>
+        <v>6982496</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7365,12 +7357,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7397,10 +7389,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117980667</v>
+        <v>117980678</v>
       </c>
       <c r="B63" t="n">
-        <v>78216</v>
+        <v>90513</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7413,21 +7405,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>1204</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7437,10 +7429,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>593125</v>
+        <v>593244</v>
       </c>
       <c r="R63" t="n">
-        <v>6982518</v>
+        <v>6982404</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7499,10 +7491,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117980678</v>
+        <v>117980620</v>
       </c>
       <c r="B64" t="n">
-        <v>90513</v>
+        <v>79590</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7511,25 +7503,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7539,10 +7531,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>593244</v>
+        <v>592968</v>
       </c>
       <c r="R64" t="n">
-        <v>6982404</v>
+        <v>6982522</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7601,10 +7593,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117980594</v>
+        <v>117980619</v>
       </c>
       <c r="B65" t="n">
-        <v>79098</v>
+        <v>79590</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7613,25 +7605,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7641,10 +7633,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>593185</v>
+        <v>592459</v>
       </c>
       <c r="R65" t="n">
-        <v>6982435</v>
+        <v>6982579</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7671,12 +7663,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7703,7 +7695,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117980643</v>
+        <v>117980653</v>
       </c>
       <c r="B66" t="n">
         <v>79561</v>
@@ -7743,10 +7735,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>592231</v>
+        <v>593140</v>
       </c>
       <c r="R66" t="n">
-        <v>6982683</v>
+        <v>6982464</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7773,12 +7765,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7805,10 +7797,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117980666</v>
+        <v>117980706</v>
       </c>
       <c r="B67" t="n">
-        <v>78216</v>
+        <v>91772</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7817,25 +7809,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7845,10 +7837,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>593185</v>
+        <v>592388</v>
       </c>
       <c r="R67" t="n">
-        <v>6982435</v>
+        <v>6982651</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7875,12 +7867,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7907,10 +7899,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117980695</v>
+        <v>117980655</v>
       </c>
       <c r="B68" t="n">
-        <v>97753</v>
+        <v>79561</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7919,25 +7911,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7947,10 +7939,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>592757</v>
+        <v>593130</v>
       </c>
       <c r="R68" t="n">
-        <v>6982507</v>
+        <v>6982511</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7977,12 +7969,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8009,10 +8001,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117980619</v>
+        <v>117980698</v>
       </c>
       <c r="B69" t="n">
-        <v>79590</v>
+        <v>97753</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8025,21 +8017,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8049,10 +8041,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>592459</v>
+        <v>593522</v>
       </c>
       <c r="R69" t="n">
-        <v>6982579</v>
+        <v>6982157</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -8079,12 +8071,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8111,10 +8103,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117980629</v>
+        <v>117980647</v>
       </c>
       <c r="B70" t="n">
-        <v>96791</v>
+        <v>79561</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8123,25 +8115,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8151,10 +8143,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>592189</v>
+        <v>592968</v>
       </c>
       <c r="R70" t="n">
-        <v>6982694</v>
+        <v>6982522</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -8181,12 +8173,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8213,7 +8205,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117980698</v>
+        <v>117980695</v>
       </c>
       <c r="B71" t="n">
         <v>97753</v>
@@ -8253,10 +8245,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>593522</v>
+        <v>592757</v>
       </c>
       <c r="R71" t="n">
-        <v>6982157</v>
+        <v>6982507</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -8283,12 +8275,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8315,10 +8307,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117980597</v>
+        <v>117980712</v>
       </c>
       <c r="B72" t="n">
-        <v>79069</v>
+        <v>79596</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8327,25 +8319,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>6463</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8355,10 +8347,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>593125</v>
+        <v>593140</v>
       </c>
       <c r="R72" t="n">
-        <v>6982518</v>
+        <v>6982464</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8417,10 +8409,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117980707</v>
+        <v>117980641</v>
       </c>
       <c r="B73" t="n">
-        <v>91772</v>
+        <v>79561</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8429,25 +8421,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8457,10 +8449,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>592286</v>
+        <v>592490</v>
       </c>
       <c r="R73" t="n">
-        <v>6982699</v>
+        <v>6982570</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8519,10 +8511,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117980600</v>
+        <v>117980694</v>
       </c>
       <c r="B74" t="n">
-        <v>90499</v>
+        <v>97753</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8531,25 +8523,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8559,10 +8551,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>592949</v>
+        <v>592218</v>
       </c>
       <c r="R74" t="n">
-        <v>6982497</v>
+        <v>6982683</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8621,10 +8613,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117980601</v>
+        <v>117980603</v>
       </c>
       <c r="B75" t="n">
-        <v>90499</v>
+        <v>57287</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8637,34 +8629,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>593259</v>
+        <v>593009</v>
       </c>
       <c r="R75" t="n">
-        <v>6982361</v>
+        <v>6982552</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8691,12 +8691,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8723,10 +8723,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>117980706</v>
+        <v>117980629</v>
       </c>
       <c r="B76" t="n">
-        <v>91772</v>
+        <v>96791</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8739,21 +8739,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8763,10 +8763,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>592388</v>
+        <v>592189</v>
       </c>
       <c r="R76" t="n">
-        <v>6982651</v>
+        <v>6982694</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>

--- a/artfynd/A 11987-2024 artfynd.xlsx
+++ b/artfynd/A 11987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117963728</v>
+        <v>117964679</v>
       </c>
       <c r="B2" t="n">
-        <v>57287</v>
+        <v>58131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>208249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592616</v>
+        <v>592525</v>
       </c>
       <c r="R2" t="n">
-        <v>6982971</v>
+        <v>6983094</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117964594</v>
+        <v>117963307</v>
       </c>
       <c r="B3" t="n">
-        <v>79561</v>
+        <v>97838</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +799,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592544</v>
+        <v>592647</v>
       </c>
       <c r="R3" t="n">
-        <v>6983091</v>
+        <v>6982916</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117964679</v>
+        <v>117963517</v>
       </c>
       <c r="B4" t="n">
-        <v>58130</v>
+        <v>97838</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +915,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592525</v>
+        <v>592623</v>
       </c>
       <c r="R4" t="n">
-        <v>6983094</v>
+        <v>6982916</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +1007,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117963209</v>
+        <v>117963188</v>
       </c>
       <c r="B5" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,7 +1054,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1060,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592669</v>
+        <v>592688</v>
       </c>
       <c r="R5" t="n">
-        <v>6982881</v>
+        <v>6982873</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117963272</v>
+        <v>117963780</v>
       </c>
       <c r="B6" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,7 +1170,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1176,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592646</v>
+        <v>592591</v>
       </c>
       <c r="R6" t="n">
-        <v>6982919</v>
+        <v>6982977</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1214,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1224,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,22 +1239,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117963188</v>
+        <v>117963272</v>
       </c>
       <c r="B7" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,7 +1286,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1292,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592688</v>
+        <v>592646</v>
       </c>
       <c r="R7" t="n">
-        <v>6982873</v>
+        <v>6982919</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,22 +1355,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117964227</v>
+        <v>117963692</v>
       </c>
       <c r="B8" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1409,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592563</v>
+        <v>592600</v>
       </c>
       <c r="R8" t="n">
-        <v>6983030</v>
+        <v>6982942</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117963446</v>
+        <v>117963209</v>
       </c>
       <c r="B9" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1516,7 +1519,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1525,10 +1528,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592644</v>
+        <v>592669</v>
       </c>
       <c r="R9" t="n">
-        <v>6982918</v>
+        <v>6982881</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1570,7 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,22 +1588,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117963692</v>
+        <v>117963141</v>
       </c>
       <c r="B10" t="n">
-        <v>57287</v>
+        <v>78482</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,39 +1616,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592600</v>
+        <v>592684</v>
       </c>
       <c r="R10" t="n">
-        <v>6982942</v>
+        <v>6982863</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1687,7 +1685,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,12 +1700,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1717,7 +1715,7 @@
         <v>117964461</v>
       </c>
       <c r="B11" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1826,10 +1824,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117963307</v>
+        <v>117964594</v>
       </c>
       <c r="B12" t="n">
-        <v>97836</v>
+        <v>79563</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,42 +1836,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592647</v>
+        <v>592544</v>
       </c>
       <c r="R12" t="n">
-        <v>6982916</v>
+        <v>6983091</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1909,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,10 +1936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117963780</v>
+        <v>117963446</v>
       </c>
       <c r="B13" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1977,7 +1971,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1986,10 +1980,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592591</v>
+        <v>592644</v>
       </c>
       <c r="R13" t="n">
-        <v>6982977</v>
+        <v>6982918</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,7 +2025,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2046,22 +2040,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117963824</v>
+        <v>117964227</v>
       </c>
       <c r="B14" t="n">
-        <v>56499</v>
+        <v>57288</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2070,31 +2064,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2103,10 +2097,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592573</v>
+        <v>592563</v>
       </c>
       <c r="R14" t="n">
-        <v>6982989</v>
+        <v>6983030</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,7 +2132,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2148,7 +2142,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,22 +2157,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117963517</v>
+        <v>117963824</v>
       </c>
       <c r="B15" t="n">
-        <v>97836</v>
+        <v>56500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2187,30 +2181,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2219,10 +2214,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592623</v>
+        <v>592573</v>
       </c>
       <c r="R15" t="n">
-        <v>6982916</v>
+        <v>6982989</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2254,7 +2249,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2264,7 +2259,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2279,22 +2274,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117963141</v>
+        <v>117963728</v>
       </c>
       <c r="B16" t="n">
-        <v>78480</v>
+        <v>57288</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2307,34 +2302,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592684</v>
+        <v>592616</v>
       </c>
       <c r="R16" t="n">
-        <v>6982863</v>
+        <v>6982971</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,10 +2403,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117980681</v>
+        <v>117980604</v>
       </c>
       <c r="B17" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2419,34 +2419,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592612</v>
+        <v>592585</v>
       </c>
       <c r="R17" t="n">
-        <v>6982945</v>
+        <v>6982972</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2505,10 +2513,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117980585</v>
+        <v>117980599</v>
       </c>
       <c r="B18" t="n">
-        <v>90464</v>
+        <v>90501</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2517,25 +2525,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2545,10 +2553,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592687</v>
+        <v>592686</v>
       </c>
       <c r="R18" t="n">
-        <v>6982838</v>
+        <v>6982827</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2607,10 +2615,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117980711</v>
+        <v>117980685</v>
       </c>
       <c r="B19" t="n">
-        <v>86816</v>
+        <v>78482</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2623,21 +2631,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2647,10 +2655,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592627</v>
+        <v>592676</v>
       </c>
       <c r="R19" t="n">
-        <v>6982939</v>
+        <v>6982878</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2709,10 +2717,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117984731</v>
+        <v>117980670</v>
       </c>
       <c r="B20" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2742,24 +2750,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden, Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592704</v>
+        <v>592638</v>
       </c>
       <c r="R20" t="n">
-        <v>6982987</v>
+        <v>6982928</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2791,40 +2799,34 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>100-tals plantor</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117980685</v>
+        <v>117984731</v>
       </c>
       <c r="B21" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2833,41 +2835,45 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Lillsjöhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592676</v>
+        <v>592704</v>
       </c>
       <c r="R21" t="n">
-        <v>6982878</v>
+        <v>6982987</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2899,34 +2905,40 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>100-tals plantor</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117980604</v>
+        <v>117980584</v>
       </c>
       <c r="B22" t="n">
-        <v>57287</v>
+        <v>90466</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2935,46 +2947,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592585</v>
+        <v>592541</v>
       </c>
       <c r="R22" t="n">
-        <v>6982972</v>
+        <v>6983087</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3033,10 +3037,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117980670</v>
+        <v>117980681</v>
       </c>
       <c r="B23" t="n">
-        <v>97836</v>
+        <v>90519</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3045,42 +3049,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592638</v>
+        <v>592612</v>
       </c>
       <c r="R23" t="n">
-        <v>6982928</v>
+        <v>6982945</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117980599</v>
+        <v>117980711</v>
       </c>
       <c r="B24" t="n">
-        <v>90499</v>
+        <v>86818</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592686</v>
+        <v>592627</v>
       </c>
       <c r="R24" t="n">
-        <v>6982827</v>
+        <v>6982939</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3241,10 +3241,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117980584</v>
+        <v>117980585</v>
       </c>
       <c r="B25" t="n">
-        <v>90464</v>
+        <v>90466</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592541</v>
+        <v>592687</v>
       </c>
       <c r="R25" t="n">
-        <v>6983087</v>
+        <v>6982838</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3346,7 +3346,7 @@
         <v>117967502</v>
       </c>
       <c r="B26" t="n">
-        <v>56491</v>
+        <v>56492</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3460,10 +3460,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117967766</v>
+        <v>117961605</v>
       </c>
       <c r="B27" t="n">
-        <v>58102</v>
+        <v>57288</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3472,20 +3472,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>208245</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3494,19 +3494,24 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
+          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592164</v>
+        <v>592958</v>
       </c>
       <c r="R27" t="n">
-        <v>6982658</v>
+        <v>6982499</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3535,7 +3540,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3545,7 +3550,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3572,10 +3577,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117961816</v>
+        <v>117961348</v>
       </c>
       <c r="B28" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3607,7 +3612,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3616,10 +3621,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592880</v>
+        <v>592940</v>
       </c>
       <c r="R28" t="n">
-        <v>6982501</v>
+        <v>6982496</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3651,7 +3656,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3661,7 +3666,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3676,22 +3681,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117962504</v>
+        <v>117967986</v>
       </c>
       <c r="B29" t="n">
-        <v>97753</v>
+        <v>57288</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3700,38 +3705,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
+          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592749</v>
+        <v>592321</v>
       </c>
       <c r="R29" t="n">
-        <v>6982429</v>
+        <v>6982713</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3763,7 +3773,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3773,7 +3783,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3788,22 +3798,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117961947</v>
+        <v>117961758</v>
       </c>
       <c r="B30" t="n">
-        <v>97836</v>
+        <v>78219</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3812,42 +3822,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592880</v>
+        <v>592907</v>
       </c>
       <c r="R30" t="n">
-        <v>6982514</v>
+        <v>6982484</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3879,7 +3885,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3889,7 +3895,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3904,22 +3910,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117967797</v>
+        <v>117961816</v>
       </c>
       <c r="B31" t="n">
-        <v>79561</v>
+        <v>97838</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3928,38 +3934,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
+          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592219</v>
+        <v>592880</v>
       </c>
       <c r="R31" t="n">
-        <v>6982668</v>
+        <v>6982501</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3991,7 +4001,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4001,7 +4011,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4028,10 +4038,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117967729</v>
+        <v>117968088</v>
       </c>
       <c r="B32" t="n">
-        <v>97740</v>
+        <v>56492</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4040,38 +4050,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220093</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svarttjärnen (Svarttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592204</v>
+        <v>592312</v>
       </c>
       <c r="R32" t="n">
-        <v>6982667</v>
+        <v>6982681</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4103,7 +4118,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4113,7 +4128,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4140,10 +4155,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117969135</v>
+        <v>117967797</v>
       </c>
       <c r="B33" t="n">
-        <v>97836</v>
+        <v>79563</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4152,42 +4167,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
+          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>593016</v>
+        <v>592219</v>
       </c>
       <c r="R33" t="n">
-        <v>6982493</v>
+        <v>6982668</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4219,7 +4230,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4229,7 +4240,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4256,10 +4267,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117968088</v>
+        <v>117969135</v>
       </c>
       <c r="B34" t="n">
-        <v>56491</v>
+        <v>97838</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4268,43 +4279,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
+          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592312</v>
+        <v>593016</v>
       </c>
       <c r="R34" t="n">
-        <v>6982681</v>
+        <v>6982493</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4336,7 +4346,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4346,7 +4356,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4373,10 +4383,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117961605</v>
+        <v>117967766</v>
       </c>
       <c r="B35" t="n">
-        <v>57287</v>
+        <v>58103</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4385,20 +4395,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>208245</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4407,24 +4417,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
+          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>592958</v>
+        <v>592164</v>
       </c>
       <c r="R35" t="n">
-        <v>6982499</v>
+        <v>6982658</v>
       </c>
       <c r="S35" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4453,7 +4458,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4463,7 +4468,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4490,10 +4495,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117961348</v>
+        <v>117962504</v>
       </c>
       <c r="B36" t="n">
-        <v>97836</v>
+        <v>97755</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4502,42 +4507,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>592940</v>
+        <v>592749</v>
       </c>
       <c r="R36" t="n">
-        <v>6982496</v>
+        <v>6982429</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4569,7 +4570,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4579,7 +4580,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4606,10 +4607,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117961466</v>
+        <v>117961947</v>
       </c>
       <c r="B37" t="n">
-        <v>57287</v>
+        <v>97838</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4618,36 +4619,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4656,10 +4651,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>592958</v>
+        <v>592880</v>
       </c>
       <c r="R37" t="n">
-        <v>6982498</v>
+        <v>6982514</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4691,7 +4686,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4701,7 +4696,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4728,10 +4723,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117962093</v>
+        <v>117962294</v>
       </c>
       <c r="B38" t="n">
-        <v>79561</v>
+        <v>91964</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4744,21 +4739,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4768,10 +4763,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>592840</v>
+        <v>592811</v>
       </c>
       <c r="R38" t="n">
-        <v>6982539</v>
+        <v>6982463</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4803,7 +4798,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4813,7 +4808,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4840,10 +4835,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117962294</v>
+        <v>117968554</v>
       </c>
       <c r="B39" t="n">
-        <v>91962</v>
+        <v>57288</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4856,34 +4851,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
+          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>592811</v>
+        <v>592461</v>
       </c>
       <c r="R39" t="n">
-        <v>6982463</v>
+        <v>6982622</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4952,10 +4952,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117961758</v>
+        <v>117962093</v>
       </c>
       <c r="B40" t="n">
-        <v>78217</v>
+        <v>79563</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4968,21 +4968,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>592907</v>
+        <v>592840</v>
       </c>
       <c r="R40" t="n">
-        <v>6982484</v>
+        <v>6982539</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5052,22 +5052,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117962152</v>
+        <v>117967729</v>
       </c>
       <c r="B41" t="n">
-        <v>57287</v>
+        <v>97742</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5076,43 +5076,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
+          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>592878</v>
+        <v>592204</v>
       </c>
       <c r="R41" t="n">
-        <v>6982510</v>
+        <v>6982667</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5144,7 +5139,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5154,7 +5149,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5169,22 +5164,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117967986</v>
+        <v>117962152</v>
       </c>
       <c r="B42" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5222,14 +5217,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
+          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>592321</v>
+        <v>592878</v>
       </c>
       <c r="R42" t="n">
-        <v>6982713</v>
+        <v>6982510</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5261,7 +5256,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5271,7 +5266,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5286,22 +5281,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117968554</v>
+        <v>117961466</v>
       </c>
       <c r="B43" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5332,21 +5327,26 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
+          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>592461</v>
+        <v>592958</v>
       </c>
       <c r="R43" t="n">
-        <v>6982622</v>
+        <v>6982498</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5415,10 +5415,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117980594</v>
+        <v>117980655</v>
       </c>
       <c r="B44" t="n">
-        <v>79098</v>
+        <v>79563</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5431,21 +5431,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>593185</v>
+        <v>593130</v>
       </c>
       <c r="R44" t="n">
-        <v>6982435</v>
+        <v>6982511</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5517,10 +5517,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117980642</v>
+        <v>117980698</v>
       </c>
       <c r="B45" t="n">
-        <v>79561</v>
+        <v>97755</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5529,25 +5529,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5557,10 +5557,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>592468</v>
+        <v>593522</v>
       </c>
       <c r="R45" t="n">
-        <v>6982583</v>
+        <v>6982157</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5587,12 +5587,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5619,10 +5619,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117980600</v>
+        <v>117980645</v>
       </c>
       <c r="B46" t="n">
-        <v>90499</v>
+        <v>79563</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5635,21 +5635,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5659,10 +5659,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>592949</v>
+        <v>592168</v>
       </c>
       <c r="R46" t="n">
-        <v>6982497</v>
+        <v>6982756</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5721,10 +5721,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117980644</v>
+        <v>117980695</v>
       </c>
       <c r="B47" t="n">
-        <v>79561</v>
+        <v>97755</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5733,25 +5733,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>592186</v>
+        <v>592757</v>
       </c>
       <c r="R47" t="n">
-        <v>6982718</v>
+        <v>6982507</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5823,10 +5823,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117980666</v>
+        <v>117980594</v>
       </c>
       <c r="B48" t="n">
-        <v>78216</v>
+        <v>79100</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5839,21 +5839,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5925,10 +5925,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117980643</v>
+        <v>117980653</v>
       </c>
       <c r="B49" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5965,10 +5965,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>592231</v>
+        <v>593140</v>
       </c>
       <c r="R49" t="n">
-        <v>6982683</v>
+        <v>6982464</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5995,12 +5995,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6027,10 +6027,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117980667</v>
+        <v>117980609</v>
       </c>
       <c r="B50" t="n">
-        <v>78216</v>
+        <v>57288</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6043,34 +6043,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>593125</v>
+        <v>593267</v>
       </c>
       <c r="R50" t="n">
-        <v>6982518</v>
+        <v>6982373</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6129,10 +6137,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117980648</v>
+        <v>117980667</v>
       </c>
       <c r="B51" t="n">
-        <v>79561</v>
+        <v>78218</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6145,21 +6153,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6169,10 +6177,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>592971</v>
+        <v>593125</v>
       </c>
       <c r="R51" t="n">
-        <v>6982531</v>
+        <v>6982518</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6231,10 +6239,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117980646</v>
+        <v>117980629</v>
       </c>
       <c r="B52" t="n">
-        <v>79561</v>
+        <v>96793</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6243,25 +6251,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6271,10 +6279,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>592988</v>
+        <v>592189</v>
       </c>
       <c r="R52" t="n">
-        <v>6982524</v>
+        <v>6982694</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6333,10 +6341,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117980624</v>
+        <v>117980608</v>
       </c>
       <c r="B53" t="n">
-        <v>57303</v>
+        <v>57288</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6349,16 +6357,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6371,7 +6379,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -6381,10 +6389,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>592180</v>
+        <v>593293</v>
       </c>
       <c r="R53" t="n">
-        <v>6982742</v>
+        <v>6982240</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6411,12 +6419,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6443,10 +6451,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117980601</v>
+        <v>117980666</v>
       </c>
       <c r="B54" t="n">
-        <v>90499</v>
+        <v>78218</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6459,21 +6467,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6483,10 +6491,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>593259</v>
+        <v>593185</v>
       </c>
       <c r="R54" t="n">
-        <v>6982361</v>
+        <v>6982435</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6545,10 +6553,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117980707</v>
+        <v>117980643</v>
       </c>
       <c r="B55" t="n">
-        <v>91772</v>
+        <v>79563</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6557,25 +6565,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6585,10 +6593,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>592286</v>
+        <v>592231</v>
       </c>
       <c r="R55" t="n">
-        <v>6982699</v>
+        <v>6982683</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6647,10 +6655,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117980608</v>
+        <v>117980707</v>
       </c>
       <c r="B56" t="n">
-        <v>57287</v>
+        <v>91774</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6659,46 +6667,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>593293</v>
+        <v>592286</v>
       </c>
       <c r="R56" t="n">
-        <v>6982240</v>
+        <v>6982699</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6725,12 +6725,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6757,10 +6757,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117980609</v>
+        <v>117980647</v>
       </c>
       <c r="B57" t="n">
-        <v>57287</v>
+        <v>79563</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6773,42 +6773,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>593267</v>
+        <v>592968</v>
       </c>
       <c r="R57" t="n">
-        <v>6982373</v>
+        <v>6982522</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6867,10 +6859,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117980597</v>
+        <v>117980603</v>
       </c>
       <c r="B58" t="n">
-        <v>79069</v>
+        <v>57288</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6883,34 +6875,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>593125</v>
+        <v>593009</v>
       </c>
       <c r="R58" t="n">
-        <v>6982518</v>
+        <v>6982552</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6937,12 +6937,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6969,10 +6969,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117980645</v>
+        <v>117980644</v>
       </c>
       <c r="B59" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>592168</v>
+        <v>592186</v>
       </c>
       <c r="R59" t="n">
-        <v>6982756</v>
+        <v>6982718</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7074,7 +7074,7 @@
         <v>117980586</v>
       </c>
       <c r="B60" t="n">
-        <v>90464</v>
+        <v>90466</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7173,10 +7173,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117980621</v>
+        <v>117980646</v>
       </c>
       <c r="B61" t="n">
-        <v>79590</v>
+        <v>79563</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7185,25 +7185,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7213,10 +7213,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>593140</v>
+        <v>592988</v>
       </c>
       <c r="R61" t="n">
-        <v>6982464</v>
+        <v>6982524</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7243,12 +7243,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7275,10 +7275,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117980607</v>
+        <v>117980601</v>
       </c>
       <c r="B62" t="n">
-        <v>57287</v>
+        <v>90501</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7291,46 +7291,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>592961</v>
+        <v>593259</v>
       </c>
       <c r="R62" t="n">
-        <v>6982496</v>
+        <v>6982361</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7389,10 +7377,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117980678</v>
+        <v>117980648</v>
       </c>
       <c r="B63" t="n">
-        <v>90513</v>
+        <v>79563</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7405,21 +7393,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7429,10 +7417,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>593244</v>
+        <v>592971</v>
       </c>
       <c r="R63" t="n">
-        <v>6982404</v>
+        <v>6982531</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7491,10 +7479,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117980620</v>
+        <v>117980694</v>
       </c>
       <c r="B64" t="n">
-        <v>79590</v>
+        <v>97755</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7507,21 +7495,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7531,10 +7519,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>592968</v>
+        <v>592218</v>
       </c>
       <c r="R64" t="n">
-        <v>6982522</v>
+        <v>6982683</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7561,12 +7549,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7593,10 +7581,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117980619</v>
+        <v>117980620</v>
       </c>
       <c r="B65" t="n">
-        <v>79590</v>
+        <v>79592</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7633,10 +7621,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>592459</v>
+        <v>592968</v>
       </c>
       <c r="R65" t="n">
-        <v>6982579</v>
+        <v>6982522</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7663,12 +7651,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7695,10 +7683,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117980653</v>
+        <v>117980624</v>
       </c>
       <c r="B66" t="n">
-        <v>79561</v>
+        <v>57304</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7711,34 +7699,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>593140</v>
+        <v>592180</v>
       </c>
       <c r="R66" t="n">
-        <v>6982464</v>
+        <v>6982742</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7765,12 +7761,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7797,10 +7793,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117980706</v>
+        <v>117980641</v>
       </c>
       <c r="B67" t="n">
-        <v>91772</v>
+        <v>79563</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7809,25 +7805,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7837,10 +7833,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>592388</v>
+        <v>592490</v>
       </c>
       <c r="R67" t="n">
-        <v>6982651</v>
+        <v>6982570</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7899,10 +7895,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117980655</v>
+        <v>117980621</v>
       </c>
       <c r="B68" t="n">
-        <v>79561</v>
+        <v>79592</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7911,25 +7907,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7939,10 +7935,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>593130</v>
+        <v>593140</v>
       </c>
       <c r="R68" t="n">
-        <v>6982511</v>
+        <v>6982464</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8001,10 +7997,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117980698</v>
+        <v>117980678</v>
       </c>
       <c r="B69" t="n">
-        <v>97753</v>
+        <v>90515</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8013,25 +8009,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219790</v>
+        <v>1204</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8041,10 +8037,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>593522</v>
+        <v>593244</v>
       </c>
       <c r="R69" t="n">
-        <v>6982157</v>
+        <v>6982404</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -8103,10 +8099,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117980647</v>
+        <v>117980642</v>
       </c>
       <c r="B70" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8143,10 +8139,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>592968</v>
+        <v>592468</v>
       </c>
       <c r="R70" t="n">
-        <v>6982522</v>
+        <v>6982583</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -8173,12 +8169,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8205,10 +8201,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117980695</v>
+        <v>117980597</v>
       </c>
       <c r="B71" t="n">
-        <v>97753</v>
+        <v>79071</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8217,25 +8213,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219790</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8245,10 +8241,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>592757</v>
+        <v>593125</v>
       </c>
       <c r="R71" t="n">
-        <v>6982507</v>
+        <v>6982518</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -8275,12 +8271,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8307,10 +8303,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117980712</v>
+        <v>117980706</v>
       </c>
       <c r="B72" t="n">
-        <v>79596</v>
+        <v>91774</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8323,21 +8319,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8347,10 +8343,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>593140</v>
+        <v>592388</v>
       </c>
       <c r="R72" t="n">
-        <v>6982464</v>
+        <v>6982651</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8377,12 +8373,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8409,10 +8405,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117980641</v>
+        <v>117980607</v>
       </c>
       <c r="B73" t="n">
-        <v>79561</v>
+        <v>57288</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8425,34 +8421,46 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>592490</v>
+        <v>592961</v>
       </c>
       <c r="R73" t="n">
-        <v>6982570</v>
+        <v>6982496</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8479,12 +8487,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8511,10 +8519,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117980694</v>
+        <v>117980619</v>
       </c>
       <c r="B74" t="n">
-        <v>97753</v>
+        <v>79592</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8527,21 +8535,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8551,10 +8559,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>592218</v>
+        <v>592459</v>
       </c>
       <c r="R74" t="n">
-        <v>6982683</v>
+        <v>6982579</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8613,10 +8621,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117980603</v>
+        <v>117980712</v>
       </c>
       <c r="B75" t="n">
-        <v>57287</v>
+        <v>79598</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8625,46 +8633,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>593009</v>
+        <v>593140</v>
       </c>
       <c r="R75" t="n">
-        <v>6982552</v>
+        <v>6982464</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8691,12 +8691,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8723,10 +8723,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>117980629</v>
+        <v>117980600</v>
       </c>
       <c r="B76" t="n">
-        <v>96791</v>
+        <v>90501</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8735,25 +8735,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8763,10 +8763,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>592189</v>
+        <v>592949</v>
       </c>
       <c r="R76" t="n">
-        <v>6982694</v>
+        <v>6982497</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>

--- a/artfynd/A 11987-2024 artfynd.xlsx
+++ b/artfynd/A 11987-2024 artfynd.xlsx
@@ -3037,10 +3037,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117980681</v>
+        <v>117980711</v>
       </c>
       <c r="B23" t="n">
-        <v>90519</v>
+        <v>86818</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3053,21 +3053,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592612</v>
+        <v>592627</v>
       </c>
       <c r="R23" t="n">
-        <v>6982945</v>
+        <v>6982939</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117980711</v>
+        <v>117980681</v>
       </c>
       <c r="B24" t="n">
-        <v>86818</v>
+        <v>90519</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592627</v>
+        <v>592612</v>
       </c>
       <c r="R24" t="n">
-        <v>6982939</v>
+        <v>6982945</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -5415,10 +5415,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117980655</v>
+        <v>117980698</v>
       </c>
       <c r="B44" t="n">
-        <v>79563</v>
+        <v>97755</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5427,25 +5427,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5455,10 +5455,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>593130</v>
+        <v>593522</v>
       </c>
       <c r="R44" t="n">
-        <v>6982511</v>
+        <v>6982157</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5517,10 +5517,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117980698</v>
+        <v>117980655</v>
       </c>
       <c r="B45" t="n">
-        <v>97755</v>
+        <v>79563</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5529,25 +5529,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5557,10 +5557,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>593522</v>
+        <v>593130</v>
       </c>
       <c r="R45" t="n">
-        <v>6982157</v>
+        <v>6982511</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117980629</v>
+        <v>117980608</v>
       </c>
       <c r="B52" t="n">
-        <v>96793</v>
+        <v>57288</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6251,38 +6251,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>592189</v>
+        <v>593293</v>
       </c>
       <c r="R52" t="n">
-        <v>6982694</v>
+        <v>6982240</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6309,12 +6317,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6341,10 +6349,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117980608</v>
+        <v>117980666</v>
       </c>
       <c r="B53" t="n">
-        <v>57288</v>
+        <v>78218</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6357,42 +6365,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>593293</v>
+        <v>593185</v>
       </c>
       <c r="R53" t="n">
-        <v>6982240</v>
+        <v>6982435</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6451,10 +6451,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117980666</v>
+        <v>117980629</v>
       </c>
       <c r="B54" t="n">
-        <v>78218</v>
+        <v>96793</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6463,25 +6463,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>593185</v>
+        <v>592189</v>
       </c>
       <c r="R54" t="n">
-        <v>6982435</v>
+        <v>6982694</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6521,12 +6521,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6553,10 +6553,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117980643</v>
+        <v>117980707</v>
       </c>
       <c r="B55" t="n">
-        <v>79563</v>
+        <v>91774</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6565,25 +6565,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6593,10 +6593,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>592231</v>
+        <v>592286</v>
       </c>
       <c r="R55" t="n">
-        <v>6982683</v>
+        <v>6982699</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6655,10 +6655,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117980707</v>
+        <v>117980643</v>
       </c>
       <c r="B56" t="n">
-        <v>91774</v>
+        <v>79563</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6667,25 +6667,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6695,10 +6695,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>592286</v>
+        <v>592231</v>
       </c>
       <c r="R56" t="n">
-        <v>6982699</v>
+        <v>6982683</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -7793,10 +7793,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117980641</v>
+        <v>117980678</v>
       </c>
       <c r="B67" t="n">
-        <v>79563</v>
+        <v>90515</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7809,21 +7809,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7833,10 +7833,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>592490</v>
+        <v>593244</v>
       </c>
       <c r="R67" t="n">
-        <v>6982570</v>
+        <v>6982404</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7863,12 +7863,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7895,10 +7895,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117980621</v>
+        <v>117980641</v>
       </c>
       <c r="B68" t="n">
-        <v>79592</v>
+        <v>79563</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7907,25 +7907,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7935,10 +7935,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>593140</v>
+        <v>592490</v>
       </c>
       <c r="R68" t="n">
-        <v>6982464</v>
+        <v>6982570</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7997,10 +7997,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117980678</v>
+        <v>117980621</v>
       </c>
       <c r="B69" t="n">
-        <v>90515</v>
+        <v>79592</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8009,25 +8009,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8037,10 +8037,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>593244</v>
+        <v>593140</v>
       </c>
       <c r="R69" t="n">
-        <v>6982404</v>
+        <v>6982464</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>

--- a/artfynd/A 11987-2024 artfynd.xlsx
+++ b/artfynd/A 11987-2024 artfynd.xlsx
@@ -2882,7 +2882,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117964227</v>
+        <v>117963728</v>
       </c>
       <c r="B22" t="n">
         <v>57290</v>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592563</v>
+        <v>592616</v>
       </c>
       <c r="R22" t="n">
-        <v>6983030</v>
+        <v>6982971</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2987,12 +2987,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3109,7 +3109,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117963728</v>
+        <v>117963692</v>
       </c>
       <c r="B24" t="n">
         <v>57290</v>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592616</v>
+        <v>592600</v>
       </c>
       <c r="R24" t="n">
-        <v>6982971</v>
+        <v>6982942</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3214,19 +3214,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117963692</v>
+        <v>117964227</v>
       </c>
       <c r="B25" t="n">
         <v>57290</v>
@@ -3271,10 +3271,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592600</v>
+        <v>592563</v>
       </c>
       <c r="R25" t="n">
-        <v>6982942</v>
+        <v>6983030</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -7791,14 +7791,14 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117961605</v>
+        <v>117961466</v>
       </c>
       <c r="B68" t="n">
         <v>57290</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7825,9 +7825,14 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7839,10 +7844,10 @@
         <v>592958</v>
       </c>
       <c r="R68" t="n">
-        <v>6982499</v>
+        <v>6982498</v>
       </c>
       <c r="S68" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7871,7 +7876,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7881,7 +7886,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7908,7 +7913,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117980607</v>
+        <v>117961605</v>
       </c>
       <c r="B69" t="n">
         <v>57290</v>
@@ -7941,32 +7946,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>592961</v>
+        <v>592958</v>
       </c>
       <c r="R69" t="n">
-        <v>6982496</v>
+        <v>6982499</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7990,12 +7988,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8010,26 +8018,26 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117961466</v>
+        <v>117980607</v>
       </c>
       <c r="B70" t="n">
         <v>57290</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8055,30 +8063,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>592958</v>
+        <v>592961</v>
       </c>
       <c r="R70" t="n">
-        <v>6982498</v>
+        <v>6982496</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8102,22 +8112,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8132,12 +8132,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8254,7 +8254,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117962152</v>
+        <v>117967986</v>
       </c>
       <c r="B72" t="n">
         <v>57290</v>
@@ -8295,14 +8295,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
+          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>592878</v>
+        <v>592321</v>
       </c>
       <c r="R72" t="n">
-        <v>6982510</v>
+        <v>6982713</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8359,19 +8359,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117968554</v>
+        <v>117962152</v>
       </c>
       <c r="B73" t="n">
         <v>57290</v>
@@ -8412,14 +8412,14 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
+          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>592461</v>
+        <v>592878</v>
       </c>
       <c r="R73" t="n">
-        <v>6982622</v>
+        <v>6982510</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8476,19 +8476,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117980609</v>
+        <v>117980603</v>
       </c>
       <c r="B74" t="n">
         <v>57290</v>
@@ -8526,7 +8526,7 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -8536,10 +8536,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>593267</v>
+        <v>593009</v>
       </c>
       <c r="R74" t="n">
-        <v>6982373</v>
+        <v>6982552</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8566,12 +8566,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8598,7 +8598,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117967986</v>
+        <v>117980609</v>
       </c>
       <c r="B75" t="n">
         <v>57290</v>
@@ -8632,24 +8632,27 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>592321</v>
+        <v>593267</v>
       </c>
       <c r="R75" t="n">
-        <v>6982713</v>
+        <v>6982373</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8673,22 +8676,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>16:16</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>16:16</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8703,19 +8696,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>117980603</v>
+        <v>117968554</v>
       </c>
       <c r="B76" t="n">
         <v>57290</v>
@@ -8749,27 +8742,24 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>593009</v>
+        <v>592461</v>
       </c>
       <c r="R76" t="n">
-        <v>6982552</v>
+        <v>6982622</v>
       </c>
       <c r="S76" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8796,9 +8786,19 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8813,12 +8813,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>

--- a/artfynd/A 11987-2024 artfynd.xlsx
+++ b/artfynd/A 11987-2024 artfynd.xlsx
@@ -2882,7 +2882,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117963728</v>
+        <v>117964227</v>
       </c>
       <c r="B22" t="n">
         <v>57290</v>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592616</v>
+        <v>592563</v>
       </c>
       <c r="R22" t="n">
-        <v>6982971</v>
+        <v>6983030</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2987,19 +2987,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117980604</v>
+        <v>117963728</v>
       </c>
       <c r="B23" t="n">
         <v>57290</v>
@@ -3033,27 +3033,24 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592585</v>
+        <v>592616</v>
       </c>
       <c r="R23" t="n">
-        <v>6982972</v>
+        <v>6982971</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3080,9 +3077,19 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3097,12 +3104,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3226,7 +3233,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117964227</v>
+        <v>117980604</v>
       </c>
       <c r="B25" t="n">
         <v>57290</v>
@@ -3260,24 +3267,27 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lillsjöhöjden (Lillsjöhöjden), Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592563</v>
+        <v>592585</v>
       </c>
       <c r="R25" t="n">
-        <v>6983030</v>
+        <v>6982972</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3304,19 +3314,9 @@
           <t>2024-06-23</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3331,12 +3331,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -7791,14 +7791,14 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117961466</v>
+        <v>117980607</v>
       </c>
       <c r="B68" t="n">
         <v>57290</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7824,30 +7824,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>592958</v>
+        <v>592961</v>
       </c>
       <c r="R68" t="n">
-        <v>6982498</v>
+        <v>6982496</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7871,22 +7873,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7901,12 +7893,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8030,14 +8022,14 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117980607</v>
+        <v>117961466</v>
       </c>
       <c r="B70" t="n">
         <v>57290</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8063,32 +8055,30 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>592961</v>
+        <v>592958</v>
       </c>
       <c r="R70" t="n">
-        <v>6982496</v>
+        <v>6982498</v>
       </c>
       <c r="S70" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8112,12 +8102,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8132,19 +8132,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117980608</v>
+        <v>117980603</v>
       </c>
       <c r="B71" t="n">
         <v>57290</v>
@@ -8182,7 +8182,7 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -8192,10 +8192,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>593293</v>
+        <v>593009</v>
       </c>
       <c r="R71" t="n">
-        <v>6982240</v>
+        <v>6982552</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -8222,12 +8222,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8254,7 +8254,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117967986</v>
+        <v>117962152</v>
       </c>
       <c r="B72" t="n">
         <v>57290</v>
@@ -8295,14 +8295,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
+          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>592321</v>
+        <v>592878</v>
       </c>
       <c r="R72" t="n">
-        <v>6982713</v>
+        <v>6982510</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8359,19 +8359,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117962152</v>
+        <v>117980608</v>
       </c>
       <c r="B73" t="n">
         <v>57290</v>
@@ -8405,24 +8405,27 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>592878</v>
+        <v>593293</v>
       </c>
       <c r="R73" t="n">
-        <v>6982510</v>
+        <v>6982240</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8446,22 +8449,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>12:24</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>12:24</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8476,19 +8469,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117980603</v>
+        <v>117967986</v>
       </c>
       <c r="B74" t="n">
         <v>57290</v>
@@ -8522,27 +8515,24 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>593009</v>
+        <v>592321</v>
       </c>
       <c r="R74" t="n">
-        <v>6982552</v>
+        <v>6982713</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8569,9 +8559,19 @@
           <t>2024-06-23</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8586,12 +8586,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>

--- a/artfynd/A 11987-2024 artfynd.xlsx
+++ b/artfynd/A 11987-2024 artfynd.xlsx
@@ -7791,7 +7791,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117980607</v>
+        <v>117961605</v>
       </c>
       <c r="B68" t="n">
         <v>57290</v>
@@ -7824,32 +7824,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>592961</v>
+        <v>592958</v>
       </c>
       <c r="R68" t="n">
-        <v>6982496</v>
+        <v>6982499</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7873,12 +7866,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7893,26 +7896,26 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117961605</v>
+        <v>117961466</v>
       </c>
       <c r="B69" t="n">
         <v>57290</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -7939,9 +7942,14 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -7953,10 +7961,10 @@
         <v>592958</v>
       </c>
       <c r="R69" t="n">
-        <v>6982499</v>
+        <v>6982498</v>
       </c>
       <c r="S69" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7985,7 +7993,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7995,7 +8003,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8022,14 +8030,14 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117961466</v>
+        <v>117980607</v>
       </c>
       <c r="B70" t="n">
         <v>57290</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8055,30 +8063,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>592958</v>
+        <v>592961</v>
       </c>
       <c r="R70" t="n">
-        <v>6982498</v>
+        <v>6982496</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8102,22 +8112,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8132,12 +8132,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8254,7 +8254,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117962152</v>
+        <v>117980609</v>
       </c>
       <c r="B72" t="n">
         <v>57290</v>
@@ -8288,24 +8288,27 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>592878</v>
+        <v>593267</v>
       </c>
       <c r="R72" t="n">
-        <v>6982510</v>
+        <v>6982373</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8329,22 +8332,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>12:24</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>12:24</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8359,19 +8352,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117980608</v>
+        <v>117962152</v>
       </c>
       <c r="B73" t="n">
         <v>57290</v>
@@ -8405,27 +8398,24 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>593293</v>
+        <v>592878</v>
       </c>
       <c r="R73" t="n">
-        <v>6982240</v>
+        <v>6982510</v>
       </c>
       <c r="S73" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8449,12 +8439,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8469,12 +8469,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8598,7 +8598,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117980609</v>
+        <v>117980608</v>
       </c>
       <c r="B75" t="n">
         <v>57290</v>
@@ -8646,10 +8646,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>593267</v>
+        <v>593293</v>
       </c>
       <c r="R75" t="n">
-        <v>6982373</v>
+        <v>6982240</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>

--- a/artfynd/A 11987-2024 artfynd.xlsx
+++ b/artfynd/A 11987-2024 artfynd.xlsx
@@ -2882,7 +2882,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117964227</v>
+        <v>117963692</v>
       </c>
       <c r="B22" t="n">
         <v>57290</v>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592563</v>
+        <v>592600</v>
       </c>
       <c r="R22" t="n">
-        <v>6983030</v>
+        <v>6982942</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2999,7 +2999,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117963728</v>
+        <v>117964227</v>
       </c>
       <c r="B23" t="n">
         <v>57290</v>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592616</v>
+        <v>592563</v>
       </c>
       <c r="R23" t="n">
-        <v>6982971</v>
+        <v>6983030</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3104,19 +3104,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117963692</v>
+        <v>117963728</v>
       </c>
       <c r="B24" t="n">
         <v>57290</v>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592600</v>
+        <v>592616</v>
       </c>
       <c r="R24" t="n">
-        <v>6982942</v>
+        <v>6982971</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3221,12 +3221,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -7791,14 +7791,14 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117961605</v>
+        <v>117961466</v>
       </c>
       <c r="B68" t="n">
         <v>57290</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7825,9 +7825,14 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7839,10 +7844,10 @@
         <v>592958</v>
       </c>
       <c r="R68" t="n">
-        <v>6982499</v>
+        <v>6982498</v>
       </c>
       <c r="S68" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7871,7 +7876,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7881,7 +7886,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7908,14 +7913,14 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117961466</v>
+        <v>117980607</v>
       </c>
       <c r="B69" t="n">
         <v>57290</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -7941,30 +7946,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>592958</v>
+        <v>592961</v>
       </c>
       <c r="R69" t="n">
-        <v>6982498</v>
+        <v>6982496</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7988,22 +7995,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8018,19 +8015,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117980607</v>
+        <v>117961605</v>
       </c>
       <c r="B70" t="n">
         <v>57290</v>
@@ -8063,32 +8060,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>592961</v>
+        <v>592958</v>
       </c>
       <c r="R70" t="n">
-        <v>6982496</v>
+        <v>6982499</v>
       </c>
       <c r="S70" t="n">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8112,12 +8102,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8132,12 +8132,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8254,7 +8254,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117980609</v>
+        <v>117967986</v>
       </c>
       <c r="B72" t="n">
         <v>57290</v>
@@ -8288,27 +8288,24 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>593267</v>
+        <v>592321</v>
       </c>
       <c r="R72" t="n">
-        <v>6982373</v>
+        <v>6982713</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8332,12 +8329,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8352,12 +8359,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8481,7 +8488,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117967986</v>
+        <v>117980608</v>
       </c>
       <c r="B74" t="n">
         <v>57290</v>
@@ -8515,24 +8522,27 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>592321</v>
+        <v>593293</v>
       </c>
       <c r="R74" t="n">
-        <v>6982713</v>
+        <v>6982240</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8556,22 +8566,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>16:16</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>16:16</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8586,19 +8586,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117980608</v>
+        <v>117968554</v>
       </c>
       <c r="B75" t="n">
         <v>57290</v>
@@ -8632,27 +8632,24 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lill-Gussjön, Jmt</t>
+          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>593293</v>
+        <v>592461</v>
       </c>
       <c r="R75" t="n">
-        <v>6982240</v>
+        <v>6982622</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8676,12 +8673,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8696,19 +8703,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>117968554</v>
+        <v>117980609</v>
       </c>
       <c r="B76" t="n">
         <v>57290</v>
@@ -8742,24 +8749,27 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Svarttjärnen (Svarttjärnen), Jmt</t>
+          <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>592461</v>
+        <v>593267</v>
       </c>
       <c r="R76" t="n">
-        <v>6982622</v>
+        <v>6982373</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8783,22 +8793,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>16:33</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>16:33</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8813,12 +8813,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>

--- a/artfynd/A 11987-2024 artfynd.xlsx
+++ b/artfynd/A 11987-2024 artfynd.xlsx
@@ -7794,7 +7794,7 @@
         <v>117961605</v>
       </c>
       <c r="B68" t="n">
-        <v>57292</v>
+        <v>57384</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
+          <t>Svarttjärnbäcken, Svarttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
@@ -7911,7 +7911,7 @@
         <v>117980607</v>
       </c>
       <c r="B69" t="n">
-        <v>57292</v>
+        <v>57384</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>117961466</v>
       </c>
       <c r="B70" t="n">
-        <v>57292</v>
+        <v>57384</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
+          <t>Svarttjärnbäcken, Svarttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">

--- a/artfynd/A 11987-2024 artfynd.xlsx
+++ b/artfynd/A 11987-2024 artfynd.xlsx
@@ -7911,12 +7911,7 @@
         <v>117980607</v>
       </c>
       <c r="B69" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 11987-2024 artfynd.xlsx
+++ b/artfynd/A 11987-2024 artfynd.xlsx
@@ -7911,7 +7911,7 @@
         <v>117980607</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 11987-2024 artfynd.xlsx
+++ b/artfynd/A 11987-2024 artfynd.xlsx
@@ -7911,7 +7911,7 @@
         <v>117980607</v>
       </c>
       <c r="B69" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 11987-2024 artfynd.xlsx
+++ b/artfynd/A 11987-2024 artfynd.xlsx
@@ -7911,7 +7911,7 @@
         <v>117980607</v>
       </c>
       <c r="B69" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
